--- a/site/docs/practicum/overview.xlsx
+++ b/site/docs/practicum/overview.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="The seven exercises, in order" sheetId="1" r:id="rId1"/>
+    <sheet name="The eight exercises, in order" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -201,6 +201,23 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">08-audit-response.md</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">CSAM</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>